--- a/research/traditional_assets/database/data/kuwait/kuwait_computer_services.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_computer_services.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.191</v>
+        <v>-0.192</v>
       </c>
       <c r="G2">
-        <v>-0.3822222222222222</v>
+        <v>-0.2628865979381443</v>
       </c>
       <c r="H2">
-        <v>-0.3822222222222222</v>
+        <v>-0.2628865979381443</v>
       </c>
       <c r="I2">
-        <v>-0.4230647668289728</v>
+        <v>-0.2110890831717796</v>
       </c>
       <c r="J2">
-        <v>-0.4230647668289728</v>
+        <v>-0.2110890831717796</v>
       </c>
       <c r="K2">
-        <v>-2.96</v>
+        <v>-1.18</v>
       </c>
       <c r="L2">
-        <v>-0.3288888888888889</v>
+        <v>-0.1216494845360825</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,70 +630,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>30.2</v>
+        <v>13</v>
       </c>
       <c r="V2">
-        <v>0.9710610932475884</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="W2">
-        <v>-0.07272727272727272</v>
+        <v>-0.03064935064935065</v>
       </c>
       <c r="X2">
-        <v>0.06616747351439427</v>
+        <v>0.1129400993632523</v>
       </c>
       <c r="Y2">
-        <v>-0.138894746241667</v>
+        <v>-0.143589450012603</v>
       </c>
       <c r="Z2">
-        <v>2.644791686856375</v>
+        <v>1.168277690752875</v>
       </c>
       <c r="AA2">
-        <v>-1.118918178311098</v>
+        <v>-0.2466106666310683</v>
       </c>
       <c r="AB2">
-        <v>0.06616360967092673</v>
+        <v>0.1129347791670348</v>
       </c>
       <c r="AC2">
-        <v>-1.185081787982025</v>
+        <v>-0.359545445798103</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0.002914507303776646</v>
+        <v>0.002820533831311376</v>
       </c>
       <c r="AF2">
-        <v>0.002914507303776646</v>
+        <v>0.002820533831311376</v>
       </c>
       <c r="AG2">
-        <v>-30.19708549269622</v>
+        <v>-12.99717946616869</v>
       </c>
       <c r="AH2">
-        <v>9.370527971236403e-05</v>
+        <v>9.039355362933435e-05</v>
       </c>
       <c r="AI2">
-        <v>7.569575812822639e-05</v>
+        <v>7.790922888661683e-05</v>
       </c>
       <c r="AJ2">
-        <v>-33.44401407711194</v>
+        <v>-0.7140200850748626</v>
       </c>
       <c r="AK2">
-        <v>-3.636925981368701</v>
+        <v>-0.5601551521384179</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.633</v>
+        <v>-0.509</v>
       </c>
       <c r="AN2">
         <v>-0</v>
       </c>
       <c r="AP2">
-        <v>8.561691378706046</v>
+        <v>6.851438832982967</v>
       </c>
       <c r="AQ2">
-        <v>6.018957345971564</v>
+        <v>4.027504911591355</v>
       </c>
     </row>
     <row r="3">
@@ -713,25 +713,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.191</v>
+        <v>-0.192</v>
       </c>
       <c r="G3">
-        <v>-0.3822222222222222</v>
+        <v>-0.2628865979381443</v>
       </c>
       <c r="H3">
-        <v>-0.3822222222222222</v>
+        <v>-0.2628865979381443</v>
       </c>
       <c r="I3">
-        <v>-0.4230647668289728</v>
+        <v>-0.2110890831717796</v>
       </c>
       <c r="J3">
-        <v>-0.4230647668289728</v>
+        <v>-0.2110890831717796</v>
       </c>
       <c r="K3">
-        <v>-2.96</v>
+        <v>-1.18</v>
       </c>
       <c r="L3">
-        <v>-0.3288888888888889</v>
+        <v>-0.1216494845360825</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,70 +755,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>30.2</v>
+        <v>13</v>
       </c>
       <c r="V3">
-        <v>0.9710610932475884</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="W3">
-        <v>-0.07272727272727272</v>
+        <v>-0.03064935064935065</v>
       </c>
       <c r="X3">
-        <v>0.06616747351439427</v>
+        <v>0.1129400993632523</v>
       </c>
       <c r="Y3">
-        <v>-0.138894746241667</v>
+        <v>-0.143589450012603</v>
       </c>
       <c r="Z3">
-        <v>2.644791686856375</v>
+        <v>1.168277690752875</v>
       </c>
       <c r="AA3">
-        <v>-1.118918178311098</v>
+        <v>-0.2466106666310683</v>
       </c>
       <c r="AB3">
-        <v>0.06616360967092673</v>
+        <v>0.1129347791670348</v>
       </c>
       <c r="AC3">
-        <v>-1.185081787982025</v>
+        <v>-0.359545445798103</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>0.002914507303776646</v>
+        <v>0.002820533831311376</v>
       </c>
       <c r="AF3">
-        <v>0.002914507303776646</v>
+        <v>0.002820533831311376</v>
       </c>
       <c r="AG3">
-        <v>-30.19708549269622</v>
+        <v>-12.99717946616869</v>
       </c>
       <c r="AH3">
-        <v>9.370527971236403e-05</v>
+        <v>9.039355362933435e-05</v>
       </c>
       <c r="AI3">
-        <v>7.569575812822639e-05</v>
+        <v>7.790922888661683e-05</v>
       </c>
       <c r="AJ3">
-        <v>-33.44401407711194</v>
+        <v>-0.7140200850748626</v>
       </c>
       <c r="AK3">
-        <v>-3.636925981368701</v>
+        <v>-0.5601551521384179</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.633</v>
+        <v>-0.509</v>
       </c>
       <c r="AN3">
         <v>-0</v>
       </c>
       <c r="AP3">
-        <v>8.561691378706046</v>
+        <v>6.851438832982967</v>
       </c>
       <c r="AQ3">
-        <v>6.018957345971564</v>
+        <v>4.027504911591355</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kuwait/kuwait_computer_services.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_computer_services.xlsx
@@ -587,26 +587,23 @@
           <t>Computer Services</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.192</v>
-      </c>
       <c r="G2">
-        <v>-0.2628865979381443</v>
+        <v>-0.1853448275862069</v>
       </c>
       <c r="H2">
-        <v>-0.2628865979381443</v>
+        <v>-0.1853448275862069</v>
       </c>
       <c r="I2">
-        <v>-0.2110890831717796</v>
+        <v>-0.1568965517241379</v>
       </c>
       <c r="J2">
-        <v>-0.2110890831717796</v>
+        <v>-0.1568965517241379</v>
       </c>
       <c r="K2">
-        <v>-1.18</v>
+        <v>-0.382</v>
       </c>
       <c r="L2">
-        <v>-0.1216494845360825</v>
+        <v>-0.03293103448275862</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,70 +627,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>13</v>
+        <v>1.52</v>
       </c>
       <c r="V2">
-        <v>0.4166666666666667</v>
+        <v>0.05868725868725869</v>
       </c>
       <c r="W2">
-        <v>-0.03064935064935065</v>
+        <v>-0.0105524861878453</v>
       </c>
       <c r="X2">
-        <v>0.1129400993632523</v>
+        <v>0.09467925274843225</v>
       </c>
       <c r="Y2">
-        <v>-0.143589450012603</v>
+        <v>-0.1052317389362776</v>
       </c>
       <c r="Z2">
-        <v>1.168277690752875</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="AA2">
-        <v>-0.2466106666310683</v>
+        <v>-0.07844827586206896</v>
       </c>
       <c r="AB2">
-        <v>0.1129347791670348</v>
+        <v>0.09467925274843225</v>
       </c>
       <c r="AC2">
-        <v>-0.359545445798103</v>
+        <v>-0.1731275286105012</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0.002820533831311376</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.002820533831311376</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>-12.99717946616869</v>
+        <v>-1.52</v>
       </c>
       <c r="AH2">
-        <v>9.039355362933435e-05</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>7.790922888661683e-05</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.7140200850748626</v>
+        <v>-0.06234618539786711</v>
       </c>
       <c r="AK2">
-        <v>-0.5601551521384179</v>
+        <v>-0.04143947655398037</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.509</v>
+        <v>-1.26</v>
       </c>
       <c r="AN2">
         <v>-0</v>
       </c>
       <c r="AP2">
-        <v>6.851438832982967</v>
+        <v>0.8994082840236687</v>
       </c>
       <c r="AQ2">
-        <v>4.027504911591355</v>
+        <v>1.444444444444444</v>
       </c>
     </row>
     <row r="3">
@@ -712,26 +709,23 @@
           <t>Computer Services</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.192</v>
-      </c>
       <c r="G3">
-        <v>-0.2628865979381443</v>
+        <v>-0.1853448275862069</v>
       </c>
       <c r="H3">
-        <v>-0.2628865979381443</v>
+        <v>-0.1853448275862069</v>
       </c>
       <c r="I3">
-        <v>-0.2110890831717796</v>
+        <v>-0.1568965517241379</v>
       </c>
       <c r="J3">
-        <v>-0.2110890831717796</v>
+        <v>-0.1568965517241379</v>
       </c>
       <c r="K3">
-        <v>-1.18</v>
+        <v>-0.382</v>
       </c>
       <c r="L3">
-        <v>-0.1216494845360825</v>
+        <v>-0.03293103448275862</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,70 +749,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>13</v>
+        <v>1.52</v>
       </c>
       <c r="V3">
-        <v>0.4166666666666667</v>
+        <v>0.05868725868725869</v>
       </c>
       <c r="W3">
-        <v>-0.03064935064935065</v>
+        <v>-0.0105524861878453</v>
       </c>
       <c r="X3">
-        <v>0.1129400993632523</v>
+        <v>0.09467925274843225</v>
       </c>
       <c r="Y3">
-        <v>-0.143589450012603</v>
+        <v>-0.1052317389362776</v>
       </c>
       <c r="Z3">
-        <v>1.168277690752875</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="AA3">
-        <v>-0.2466106666310683</v>
+        <v>-0.07844827586206896</v>
       </c>
       <c r="AB3">
-        <v>0.1129347791670348</v>
+        <v>0.09467925274843225</v>
       </c>
       <c r="AC3">
-        <v>-0.359545445798103</v>
+        <v>-0.1731275286105012</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>0.002820533831311376</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.002820533831311376</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-12.99717946616869</v>
+        <v>-1.52</v>
       </c>
       <c r="AH3">
-        <v>9.039355362933435e-05</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>7.790922888661683e-05</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.7140200850748626</v>
+        <v>-0.06234618539786711</v>
       </c>
       <c r="AK3">
-        <v>-0.5601551521384179</v>
+        <v>-0.04143947655398037</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.509</v>
+        <v>-1.26</v>
       </c>
       <c r="AN3">
         <v>-0</v>
       </c>
       <c r="AP3">
-        <v>6.851438832982967</v>
+        <v>0.8994082840236687</v>
       </c>
       <c r="AQ3">
-        <v>4.027504911591355</v>
+        <v>1.444444444444444</v>
       </c>
     </row>
   </sheetData>
